--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:45</t>
+    <t xml:space="preserve">2026-09-09 22:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:32</t>
+    <t xml:space="preserve">2026-09-12 19:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:49</t>
+    <t xml:space="preserve">2026-09-24 00:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:27</t>
+    <t xml:space="preserve">2026-09-27 23:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -517,7 +517,7 @@
         <v>2019</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.83</v>
+        <v>8.28</v>
       </c>
     </row>
     <row r="3">
@@ -534,7 +534,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.7</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="4">
@@ -551,7 +551,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.54</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="5">
@@ -568,7 +568,7 @@
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="6">
@@ -585,7 +585,7 @@
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="7">
@@ -602,7 +602,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.28</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="8">
@@ -619,7 +619,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.3</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="9">
@@ -636,7 +636,7 @@
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.37</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="10">
@@ -653,7 +653,7 @@
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.45</v>
+        <v>-4.51</v>
       </c>
     </row>
     <row r="11">
@@ -670,7 +670,7 @@
         <v>2019</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.61</v>
+        <v>-6.11</v>
       </c>
     </row>
     <row r="12">
@@ -687,7 +687,7 @@
         <v>2019</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.83</v>
+        <v>-8.26</v>
       </c>
     </row>
     <row r="13">
@@ -704,7 +704,7 @@
         <v>2019</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-2.25</v>
+        <v>-22.52</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:09</t>
+    <t xml:space="preserve">2026-10-01 20:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:56</t>
+    <t xml:space="preserve">2026-10-02 13:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2019_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:32</t>
+    <t xml:space="preserve">2026-10-05 08:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
